--- a/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-AbridgedMortalityTable-GKS-1978-1979.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-AbridgedMortalityTable-GKS-1978-1979.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB3A237-A3FD-48DE-8113-C248CD91C46D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707B12E1-77DA-4881-A741-3B4B7627DCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="10" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="38">
   <si>
     <t>возраст</t>
   </si>
@@ -135,6 +135,15 @@
   <si>
     <t>хотя по Tx/lx получается около 52.19.</t>
   </si>
+  <si>
+    <t>Внимание!!!</t>
+  </si>
+  <si>
+    <t>Значения qx относятся не к году в среднем,</t>
+  </si>
+  <si>
+    <t>а ко всей (пятилетней) корзине в целом.</t>
+  </si>
 </sst>
 </file>
 
@@ -143,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -152,6 +161,12 @@
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -194,23 +209,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,27 +439,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D92002-F185-43F6-BB04-A28BF9ED905A}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -454,14 +485,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -513,7 +544,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -539,7 +570,7 @@
         <v>68.33</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -565,7 +596,7 @@
         <v>67.52</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -591,7 +622,7 @@
         <v>66.599999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -617,7 +648,7 @@
         <v>65.66</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -643,7 +674,7 @@
         <v>64.709999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -669,7 +700,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -695,7 +726,7 @@
         <v>55.07</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -721,7 +752,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -747,7 +778,7 @@
         <v>45.86</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -773,7 +804,7 @@
         <v>41.44</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -799,7 +830,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -825,7 +856,7 @@
         <v>32.92</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -851,7 +882,7 @@
         <v>28.86</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -877,7 +908,7 @@
         <v>25.01</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -903,7 +934,7 @@
         <v>21.29</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -929,7 +960,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -955,7 +986,7 @@
         <v>14.36</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -981,7 +1012,7 @@
         <v>11.26</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1007,7 +1038,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -1033,7 +1064,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -1059,7 +1090,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -1094,14 +1125,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1153,7 +1184,7 @@
         <v>62.46</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1179,7 +1210,7 @@
         <v>63.07</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1205,7 +1236,7 @@
         <v>62.23</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1231,7 +1262,7 @@
         <v>61.29</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1257,7 +1288,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1283,7 +1314,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1309,7 +1340,7 @@
         <v>54.59</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1335,7 +1366,7 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1361,7 +1392,7 @@
         <v>45.09</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1387,7 +1418,7 @@
         <v>40.67</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1413,7 +1444,7 @@
         <v>36.39</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1439,7 +1470,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1465,7 +1496,7 @@
         <v>28.21</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1491,7 +1522,7 @@
         <v>24.37</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1517,7 +1548,7 @@
         <v>20.77</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1543,7 +1574,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1569,7 +1600,7 @@
         <v>14.28</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1595,7 +1626,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1621,7 +1652,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1647,7 +1678,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -1673,7 +1704,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -1699,7 +1730,7 @@
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -1733,14 +1764,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1766,7 +1797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1792,7 +1823,7 @@
         <v>73.17</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1818,7 +1849,7 @@
         <v>73.55</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1844,7 +1875,7 @@
         <v>72.7</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1870,7 +1901,7 @@
         <v>71.760000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1896,7 +1927,7 @@
         <v>70.81</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1922,7 +1953,7 @@
         <v>69.84</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1948,7 +1979,7 @@
         <v>64.97</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1974,7 +2005,7 @@
         <v>60.08</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -2000,7 +2031,7 @@
         <v>55.22</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2026,7 +2057,7 @@
         <v>50.39</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -2052,7 +2083,7 @@
         <v>45.59</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2078,7 +2109,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2104,7 +2135,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2130,7 +2161,7 @@
         <v>31.63</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -2156,7 +2187,7 @@
         <v>27.23</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -2182,7 +2213,7 @@
         <v>23.01</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2208,7 +2239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -2234,7 +2265,7 @@
         <v>15.24</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2260,7 +2291,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2286,7 +2317,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -2312,7 +2343,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -2338,7 +2369,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -2372,14 +2403,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2405,7 +2436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2431,7 +2462,7 @@
         <v>68.17</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -2457,7 +2488,7 @@
         <v>68.72</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2483,7 +2514,7 @@
         <v>67.87</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2509,7 +2540,7 @@
         <v>66.94</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -2535,7 +2566,7 @@
         <v>65.989999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -2561,7 +2592,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2587,7 +2618,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -2613,7 +2644,7 @@
         <v>55.34</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -2639,7 +2670,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2665,7 +2696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -2691,7 +2722,7 @@
         <v>41.49</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2717,7 +2748,7 @@
         <v>37.08</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2743,7 +2774,7 @@
         <v>32.81</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2769,7 +2800,7 @@
         <v>28.66</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -2795,7 +2826,7 @@
         <v>24.73</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -2821,7 +2852,7 @@
         <v>20.96</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2847,7 +2878,7 @@
         <v>17.34</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -2873,7 +2904,7 @@
         <v>14.03</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2899,7 +2930,7 @@
         <v>10.99</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2925,7 +2956,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -2951,7 +2982,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -2977,7 +3008,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -3011,14 +3042,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3044,7 +3075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3070,7 +3101,7 @@
         <v>59.62</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -3096,7 +3127,7 @@
         <v>60.37</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3122,7 +3153,7 @@
         <v>59.64</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -3148,7 +3179,7 @@
         <v>58.75</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3174,7 +3205,7 @@
         <v>57.83</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3200,7 +3231,7 @@
         <v>56.9</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -3226,7 +3257,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -3252,7 +3283,7 @@
         <v>47.39</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -3278,7 +3309,7 @@
         <v>42.92</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -3304,7 +3335,7 @@
         <v>38.880000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -3330,7 +3361,7 @@
         <v>34.979999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -3356,7 +3387,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -3382,7 +3413,7 @@
         <v>27.64</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -3408,7 +3439,7 @@
         <v>24.14</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -3434,7 +3465,7 @@
         <v>20.78</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -3460,7 +3491,7 @@
         <v>17.61</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -3486,7 +3517,7 @@
         <v>14.65</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -3512,7 +3543,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -3538,7 +3569,7 @@
         <v>9.36</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -3564,7 +3595,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -3590,7 +3621,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -3616,7 +3647,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -3651,14 +3682,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3684,7 +3715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3710,7 +3741,7 @@
         <v>72.61</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -3736,7 +3767,7 @@
         <v>73.2</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3762,7 +3793,7 @@
         <v>72.489999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -3788,7 +3819,7 @@
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3814,7 +3845,7 @@
         <v>70.67</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3840,7 +3871,7 @@
         <v>69.73</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -3866,7 +3897,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -3892,7 +3923,7 @@
         <v>60.08</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -3918,7 +3949,7 @@
         <v>55.35</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -3944,7 +3975,7 @@
         <v>50.66</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -3970,7 +4001,7 @@
         <v>45.99</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -3996,7 +4027,7 @@
         <v>41.42</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -4022,7 +4053,7 @@
         <v>36.93</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -4048,7 +4079,7 @@
         <v>32.520000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -4074,7 +4105,7 @@
         <v>28.24</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -4100,7 +4131,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -4126,7 +4157,7 @@
         <v>20.07</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -4152,7 +4183,7 @@
         <v>16.23</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -4178,7 +4209,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -4204,7 +4235,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -4230,7 +4261,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -4256,7 +4287,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -4290,14 +4321,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4323,7 +4354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -4349,7 +4380,7 @@
         <v>66.319999999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -4375,7 +4406,7 @@
         <v>67.02</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4401,7 +4432,7 @@
         <v>66.31</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4427,7 +4458,7 @@
         <v>65.42</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4453,7 +4484,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -4479,7 +4510,7 @@
         <v>63.57</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -4505,7 +4536,7 @@
         <v>58.82</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -4531,7 +4562,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -4557,7 +4588,7 @@
         <v>49.45</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -4583,7 +4614,7 @@
         <v>45.18</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -4609,7 +4640,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -4635,7 +4666,7 @@
         <v>36.93</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -4661,7 +4692,7 @@
         <v>32.99</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -4687,7 +4718,7 @@
         <v>29.15</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -4713,7 +4744,7 @@
         <v>25.45</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -4739,7 +4770,7 @@
         <v>21.82</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -4765,7 +4796,7 @@
         <v>18.28</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -4791,7 +4822,7 @@
         <v>14.88</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -4817,7 +4848,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -4843,7 +4874,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -4869,7 +4900,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -4895,7 +4926,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -4929,14 +4960,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4962,7 +4993,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -4988,7 +5019,7 @@
         <v>61.66</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -5014,7 +5045,7 @@
         <v>62.31</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -5040,7 +5071,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -5066,7 +5097,7 @@
         <v>60.59</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -5092,7 +5123,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -5118,7 +5149,7 @@
         <v>58.7</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -5144,7 +5175,7 @@
         <v>53.93</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -5170,7 +5201,7 @@
         <v>49.11</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -5196,7 +5227,7 @@
         <v>44.51</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -5222,7 +5253,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -5248,7 +5279,7 @@
         <v>36.01</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -5274,7 +5305,7 @@
         <v>31.92</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -5300,7 +5331,7 @@
         <v>28.04</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -5326,7 +5357,7 @@
         <v>24.31</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -5352,7 +5383,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -5378,7 +5409,7 @@
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -5404,7 +5435,7 @@
         <v>14.42</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -5430,7 +5461,7 @@
         <v>11.65</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -5456,7 +5487,7 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -5482,7 +5513,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -5508,7 +5539,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -5534,7 +5565,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -5568,14 +5599,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5601,7 +5632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -5627,7 +5658,7 @@
         <v>73.11</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -5653,7 +5684,7 @@
         <v>73.56</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -5679,7 +5710,7 @@
         <v>72.760000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -5705,7 +5736,7 @@
         <v>71.83</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -5731,7 +5762,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -5757,7 +5788,7 @@
         <v>69.930000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -5783,7 +5814,7 @@
         <v>65.09</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -5809,7 +5840,7 @@
         <v>60.21</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -5835,7 +5866,7 @@
         <v>55.38</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -5861,7 +5892,7 @@
         <v>50.58</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -5887,7 +5918,7 @@
         <v>45.82</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -5913,7 +5944,7 @@
         <v>41.12</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -5939,7 +5970,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -5965,7 +5996,7 @@
         <v>31.98</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -5991,7 +6022,7 @@
         <v>27.62</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -6017,7 +6048,7 @@
         <v>23.42</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -6043,7 +6074,7 @@
         <v>19.41</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -6069,7 +6100,7 @@
         <v>15.63</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -6095,7 +6126,7 @@
         <v>12.12</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -6121,7 +6152,7 @@
         <v>9.0399999999999991</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -6147,7 +6178,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -6173,7 +6204,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
@@ -6202,4 +6233,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>